--- a/nriss-patch-2/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -663,7 +663,7 @@
   &lt;coding&gt;
     &lt;system value="https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis"/&gt;
     &lt;code value="GEN-295"/&gt;
-    &lt;display value="En rapport avec la prévention"/&gt;
+    &lt;display value="En rapport avec la prevention"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
